--- a/salida/excel/reporte_cursos.xlsx
+++ b/salida/excel/reporte_cursos.xlsx
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7">
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13">
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="21"/>
@@ -724,7 +724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E71"/>
+  <dimension ref="A1:E69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -814,11 +814,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5109</v>
+        <v>1366</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Introducción a la Vida Universitaria</t>
+          <t>Historia de la Educación</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -837,11 +837,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1366</v>
+        <v>9166</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Historia de la Educación</t>
+          <t>Fundamentos Neurobiológicos del Aprendizaje</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -860,11 +860,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9166</v>
+        <v>5881</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fundamentos Neurobiológicos del Aprendizaje</t>
+          <t>Familia y Escuela</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -883,15 +883,15 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5881</v>
+        <v>2533</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Familia y Escuela</t>
+          <t>Comunicación II</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -906,11 +906,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2533</v>
+        <v>9584</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Comunicación II</t>
+          <t>Lógica</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -929,11 +929,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9584</v>
+        <v>7720</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lógica</t>
+          <t>Filosofía de la Educación</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -952,15 +952,15 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7720</v>
+        <v>5448</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Filosofía de la Educación</t>
+          <t>Antropología</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -975,11 +975,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5448</v>
+        <v>4490</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Antropología</t>
+          <t>Filosofía de la Naturaleza</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -998,11 +998,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4490</v>
+        <v>8330</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Filosofía de la Naturaleza</t>
+          <t>Epistemología de la Educación</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1021,15 +1021,15 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8330</v>
+        <v>3064</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Epistemología de la Educación</t>
+          <t>Moral</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1044,11 +1044,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3064</v>
+        <v>2434</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Moral</t>
+          <t>Antropología Pedagógica</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1067,11 +1067,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2434</v>
+        <v>8518</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Antropología Pedagógica</t>
+          <t>Teorías y Enfoques Curriculares</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1090,15 +1090,15 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8518</v>
+        <v>4604</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Teorías y Enfoques Curriculares</t>
+          <t>Análisis de la Realidad Peruana</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1113,11 +1113,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4604</v>
+        <v>8588</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Análisis de la Realidad Peruana</t>
+          <t>Sociología de la Educación</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1136,11 +1136,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>8588</v>
+        <v>3079</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sociología de la Educación</t>
+          <t>Planificación de la Enseñanza</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1159,11 +1159,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3079</v>
+        <v>1512</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Planificación de la Enseñanza</t>
+          <t>Evaluación</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1182,11 +1182,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1512</v>
+        <v>1793</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Evaluación</t>
+          <t>Educación de la Afectividad</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1205,11 +1205,11 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1793</v>
+        <v>4202</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Educación de la Afectividad</t>
+          <t>Introducción a la Investigación Científica</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1228,15 +1228,15 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4202</v>
+        <v>5423</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Introducción a la Investigación Científica</t>
+          <t>Fe y Razón</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1251,11 +1251,11 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5423</v>
+        <v>6776</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Fe y Razón</t>
+          <t>Metodología de la Investigación Cualitativa</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1274,15 +1274,15 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>6776</v>
+        <v>1822</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Metodología de la Investigación Cualitativa</t>
+          <t>Educación en Virtudes</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1297,11 +1297,11 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1822</v>
+        <v>3762</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Educación en Virtudes</t>
+          <t>Inclusión y Dignidad de la Persona</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1320,11 +1320,11 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3762</v>
+        <v>9807</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Inclusión y Dignidad de la Persona</t>
+          <t>Metodología de la Investigación Cuantitativa</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1343,15 +1343,15 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>9807</v>
+        <v>7773</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Metodología de la Investigación Cuantitativa</t>
+          <t>Enseñanza Social de la Iglesia</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1366,11 +1366,11 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>7773</v>
+        <v>1240</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Enseñanza Social de la Iglesia</t>
+          <t>Ética Profesional</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1389,11 +1389,11 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1240</v>
+        <v>2632</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ética Profesional</t>
+          <t>Educación en el Bien, la Verdad y la Belleza</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1412,11 +1412,12 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2632</v>
+        <v>5166</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Educación en el Bien, la Verdad y la Belleza</t>
+          <t>Taller de Investigación Cualitativa
+Taller de Investigación Cuantitativa</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1435,773 +1436,773 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>5166</v>
+        <v>3312</v>
       </c>
       <c r="C31" t="inlineStr">
+        <is>
+          <t>Taller de Proyectos Educativos</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>9</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Equivale a Educación Inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>LLYA</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1087</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Taller de Tesis I</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>9</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Equivale a Educación Inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>LLYA</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1490</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Electivo</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>9</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Equivale a Educación Inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>LLYA</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>9845</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Gestión y Políticas Públicas Educativas</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Equivale a Educación Inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>LLYA</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>8373</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Taller de Tesis II</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Equivale a Educación Inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>MYC</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>4337</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Historia de la Educación</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Equivale a Educación Inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>MYC</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>8012</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Fundamentos Neurobiológicos del Aprendizaje</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Equivale a Educación Inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>MYC</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>7821</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Comunicación I</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Equivale a Educación Inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>MYC</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>9160</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Literatura y Teatro</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Equivale a Educación Inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>MYC</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>2557</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Familia y Escuela</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Equivale a Educación Inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>MYC</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>4072</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Filosofía de la Educación</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>2</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Equivale a Educación Inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>MYC</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>7854</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Comunicación II</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>2</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Equivale a Educación Inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>MYC</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>9296</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Lógica</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>2</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Equivale a Educación Inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>MYC</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>2778</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Música y Artes Visuales</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>2</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Equivale a Educación Inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>MYC</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>8518</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Teorías y Enfoques Curriculares</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>3</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Equivale a Educación Inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>MYC</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>6469</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Epistemología de la Educación</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>3</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Equivale a Educación Inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>MYC</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>8401</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Filosofía de la Naturaleza</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>3</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Equivale a Educación Inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>MYC</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>8762</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Antropología</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>3</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Equivale a Educación Inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>MYC</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>3079</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Planificación de la Enseñanza</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>4</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Equivale a Educación Inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>MYC</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>1512</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Evaluación</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>4</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Equivale a Educación Inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>MYC</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>3132</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Antropología Pedagógica</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>4</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Equivale a Educación Inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>MYC</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1793</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Educación de la Afectividad</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>4</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Equivale a Educación Inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>MYC</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>9953</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Sociología de la Educación</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>5</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Equivale a Educación Inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>MYC</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>3064</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Moral</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>5</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Equivale a Educación Inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>MYC</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>2301</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Análisis de la Realidad Peruana</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>5</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Equivale a Educación Inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>MYC</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>2738</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Introducción a la Investigación Científica</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>5</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Equivale a Educación Inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>MYC</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>2123</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Metodología de la Investigación Cualitativa</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>6</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Equivale a Educación Inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>MYC</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>5358</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Educación en Virtudes</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>7</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Equivale a Educación Inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>MYC</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>7408</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Inclusión y Dignidad de la Persona</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>7</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Equivale a Educación Inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>MYC</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>3681</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Metodología de la Investigación Cuantitativa</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>7</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Equivale a Educación Inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>MYC</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>9639</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Educación en el Bien, la Verdad y la Belleza</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>8</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Equivale a Educación Inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>MYC</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>4966</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ética Profesional</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>8</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Equivale a Educación Inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>MYC</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>7748</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Enseñanza Social de la Iglesia</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>8</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Equivale a Educación Inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>MYC</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>3480</v>
+      </c>
+      <c r="C64" t="inlineStr">
         <is>
           <t>Taller de Investigación Cualitativa
 Taller de Investigación Cuantitativa</t>
         </is>
       </c>
-      <c r="D31" t="n">
-        <v>8</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>LLYA</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>3312</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Taller de Proyectos Educativos</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>9</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>LLYA</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>1087</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Taller de Tesis I</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>9</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>LLYA</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>1490</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Electivo</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>9</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>LLYA</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>9845</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Gestión y Políticas Públicas Educativas</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>10</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>LLYA</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>8373</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Taller de Tesis II</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>10</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>MYC</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>4337</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Historia de la Educación</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>1</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>MYC</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>8012</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Fundamentos Neurobiológicos del Aprendizaje</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>1</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>MYC</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>5557</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Introducción a la Vida Universitaria</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>1</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>MYC</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>7821</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Comunicación I</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>MYC</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>9160</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Literatura y Teatro</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>MYC</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>2557</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Familia y Escuela</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>1</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>MYC</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>4072</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Filosofía de la Educación</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>2</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>MYC</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>7854</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Comunicación II</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>2</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>MYC</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>9296</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Lógica</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>2</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>MYC</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>2778</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Música y Artes Visuales</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>2</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>MYC</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>8518</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Teorías y Enfoques Curriculares</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>3</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>MYC</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>6469</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Epistemología de la Educación</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>3</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>MYC</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>8401</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Filosofía de la Naturaleza</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>3</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>MYC</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>8762</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Antropología</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>3</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>MYC</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>3079</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Planificación de la Enseñanza</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>4</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>MYC</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>1512</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Evaluación</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>4</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>MYC</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>3132</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Antropología Pedagógica</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>4</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>MYC</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>1793</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Educación de la Afectividad</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>4</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>MYC</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>9953</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Sociología de la Educación</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>5</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>MYC</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>3064</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Moral</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>5</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>MYC</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>2301</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Análisis de la Realidad Peruana</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>5</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>MYC</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>2738</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Introducción a la Investigación Científica</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>5</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>MYC</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>2123</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Metodología de la Investigación Cualitativa</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>6</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>MYC</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>5358</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Educación en Virtudes</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>7</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>MYC</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
-        <v>7408</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Inclusión y Dignidad de la Persona</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>7</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>MYC</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>3681</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Metodología de la Investigación Cuantitativa</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>7</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>MYC</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>9639</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Educación en el Bien, la Verdad y la Belleza</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>8</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>MYC</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>4966</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ética Profesional</t>
-        </is>
-      </c>
       <c r="D64" t="n">
         <v>8</v>
       </c>
@@ -2218,15 +2219,15 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>7748</v>
+        <v>3322</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Enseñanza Social de la Iglesia</t>
+          <t>Taller de Proyectos Educativos</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2241,16 +2242,15 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>3480</v>
+        <v>6759</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Taller de Investigación Cualitativa
-Taller de Investigación Cuantitativa</t>
+          <t>Taller de Tesis I</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2265,11 +2265,11 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>3322</v>
+        <v>2791</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Taller de Proyectos Educativos</t>
+          <t>Electivo</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2288,15 +2288,15 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>6759</v>
+        <v>7324</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Taller de Tesis I</t>
+          <t>Gestión y Políticas Públicas Educativas</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2311,63 +2311,17 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>2791</v>
+        <v>3256</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Electivo</t>
+          <t>Taller de Tesis II</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E69" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>MYC</t>
-        </is>
-      </c>
-      <c r="B70" t="n">
-        <v>7324</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Gestión y Políticas Públicas Educativas</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>10</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>MYC</t>
-        </is>
-      </c>
-      <c r="B71" t="n">
-        <v>3256</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Taller de Tesis II</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>10</v>
-      </c>
-      <c r="E71" t="inlineStr">
         <is>
           <t>Equivale a Educación Inicial</t>
         </is>
@@ -2384,7 +2338,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -2442,20 +2396,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Psicología del Desarrollo</t>
+          <t>Introducción a la Vida Universitaria</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7187</v>
+        <v>5109</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2381</v>
+        <v>5557</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2463,7 +2417,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -2474,28 +2428,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Geometría Euclidiana</t>
+          <t>Psicología del Desarrollo</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1909</v>
+        <v>7187</v>
       </c>
       <c r="C3" t="n">
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>5469</v>
+        <v>2381</v>
       </c>
       <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Aula</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
         <v>3</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Aula</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>2</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -2527,7 +2481,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -2538,20 +2492,20 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Tutoría</t>
+          <t>Geometría Euclidiana</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8636</v>
+        <v>1909</v>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>8636</v>
+        <v>5469</v>
       </c>
       <c r="E5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -2559,7 +2513,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -2602,20 +2556,20 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Gestión de Instituciones Educativas y Liderazgo Pedagógico</t>
+          <t>Tutoría</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9935</v>
+        <v>8636</v>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>2283</v>
+        <v>8636</v>
       </c>
       <c r="E7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -2666,17 +2620,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Práctica de Ayudantía</t>
+          <t>Gestión de Instituciones Educativas y Liderazgo Pedagógico</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6050</v>
+        <v>9935</v>
       </c>
       <c r="C9" t="n">
         <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>1433</v>
+        <v>2283</v>
       </c>
       <c r="E9" t="n">
         <v>8</v>
@@ -2687,7 +2641,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -2719,7 +2673,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -2730,28 +2684,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Quechua</t>
+          <t>Práctica de Ayudantía</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6053</v>
+        <v>6050</v>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D11" t="n">
-        <v>1127</v>
+        <v>1433</v>
       </c>
       <c r="E11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Virtual</t>
+          <t>Aula</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -2786,6 +2740,38 @@
         <v>2</v>
       </c>
       <c r="H12" t="inlineStr">
+        <is>
+          <t>Fase prematuro: solo LLYA activo → cuenta sin fusión. Fase compartida: ambos activos → sección combinada LLYA+MYC. Fase solo MYC: MYC activo → cuenta sin fusión.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Quechua</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>6053</v>
+      </c>
+      <c r="C13" t="n">
+        <v>10</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1127</v>
+      </c>
+      <c r="E13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" t="inlineStr">
         <is>
           <t>Fase prematuro: solo LLYA activo → cuenta sin fusión. Fase compartida: ambos activos → sección combinada LLYA+MYC. Fase solo MYC: MYC activo → cuenta sin fusión.</t>
         </is>

--- a/salida/excel/reporte_cursos.xlsx
+++ b/salida/excel/reporte_cursos.xlsx
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7">
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13">
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21"/>
@@ -724,7 +724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E69"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1021,11 +1021,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3064</v>
+        <v>2434</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Moral</t>
+          <t>Antropología Pedagógica</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1044,11 +1044,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2434</v>
+        <v>8518</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Antropología Pedagógica</t>
+          <t>Teorías y Enfoques Curriculares</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1067,15 +1067,15 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8518</v>
+        <v>4604</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Teorías y Enfoques Curriculares</t>
+          <t>Análisis de la Realidad Peruana</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1090,11 +1090,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4604</v>
+        <v>8588</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Análisis de la Realidad Peruana</t>
+          <t>Sociología de la Educación</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1113,11 +1113,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>8588</v>
+        <v>3079</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sociología de la Educación</t>
+          <t>Planificación de la Enseñanza</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1136,11 +1136,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3079</v>
+        <v>1512</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Planificación de la Enseñanza</t>
+          <t>Evaluación</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1159,11 +1159,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1512</v>
+        <v>1793</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Evaluación</t>
+          <t>Educación de la Afectividad</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1182,11 +1182,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1793</v>
+        <v>4202</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Educación de la Afectividad</t>
+          <t>Introducción a la Investigación Científica</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1205,15 +1205,15 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4202</v>
+        <v>5423</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Introducción a la Investigación Científica</t>
+          <t>Fe y Razón</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1228,11 +1228,11 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5423</v>
+        <v>6776</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Fe y Razón</t>
+          <t>Metodología de la Investigación Cualitativa</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1251,15 +1251,15 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>6776</v>
+        <v>1822</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Metodología de la Investigación Cualitativa</t>
+          <t>Educación en Virtudes</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1274,11 +1274,11 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1822</v>
+        <v>3762</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Educación en Virtudes</t>
+          <t>Inclusión y Dignidad de la Persona</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1297,11 +1297,11 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3762</v>
+        <v>9807</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Inclusión y Dignidad de la Persona</t>
+          <t>Metodología de la Investigación Cuantitativa</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1320,15 +1320,15 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>9807</v>
+        <v>7773</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Metodología de la Investigación Cuantitativa</t>
+          <t>Enseñanza Social de la Iglesia</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1343,11 +1343,11 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7773</v>
+        <v>1240</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Enseñanza Social de la Iglesia</t>
+          <t>Ética Profesional</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1366,11 +1366,11 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1240</v>
+        <v>2632</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ética Profesional</t>
+          <t>Educación en el Bien, la Verdad y la Belleza</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1389,11 +1389,12 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2632</v>
+        <v>5166</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Educación en el Bien, la Verdad y la Belleza</t>
+          <t>Taller de Investigación Cualitativa
+Taller de Investigación Cuantitativa</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1412,750 +1413,750 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>5166</v>
+        <v>3312</v>
       </c>
       <c r="C30" t="inlineStr">
+        <is>
+          <t>Taller de Proyectos Educativos</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>9</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Equivale a Educación Inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>LLYA</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1087</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Taller de Tesis I</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>9</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Equivale a Educación Inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>LLYA</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1490</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Electivo</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>9</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Equivale a Educación Inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>LLYA</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>9845</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Gestión y Políticas Públicas Educativas</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Equivale a Educación Inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>LLYA</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>8373</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Taller de Tesis II</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Equivale a Educación Inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>MYC</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>4337</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Historia de la Educación</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Equivale a Educación Inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>MYC</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>8012</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Fundamentos Neurobiológicos del Aprendizaje</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Equivale a Educación Inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>MYC</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>7821</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Comunicación I</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Equivale a Educación Inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>MYC</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>9160</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Literatura y Teatro</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Equivale a Educación Inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>MYC</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>2557</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Familia y Escuela</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Equivale a Educación Inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>MYC</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>4072</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Filosofía de la Educación</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>2</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Equivale a Educación Inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>MYC</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>7854</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Comunicación II</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>2</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Equivale a Educación Inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>MYC</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>9296</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Lógica</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>2</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Equivale a Educación Inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>MYC</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>2778</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Música y Artes Visuales</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>2</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Equivale a Educación Inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>MYC</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>8518</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Teorías y Enfoques Curriculares</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>3</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Equivale a Educación Inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>MYC</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>6469</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Epistemología de la Educación</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>3</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Equivale a Educación Inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>MYC</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>8401</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Filosofía de la Naturaleza</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>3</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Equivale a Educación Inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>MYC</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>8762</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Antropología</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>3</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Equivale a Educación Inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>MYC</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>3079</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Planificación de la Enseñanza</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>4</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Equivale a Educación Inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>MYC</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1512</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Evaluación</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>4</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Equivale a Educación Inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>MYC</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>3132</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Antropología Pedagógica</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>4</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Equivale a Educación Inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>MYC</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1793</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Educación de la Afectividad</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>4</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Equivale a Educación Inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>MYC</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>9953</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Sociología de la Educación</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>5</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Equivale a Educación Inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>MYC</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>2301</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Análisis de la Realidad Peruana</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>5</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Equivale a Educación Inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>MYC</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>2738</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Introducción a la Investigación Científica</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>5</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Equivale a Educación Inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>MYC</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>2123</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Metodología de la Investigación Cualitativa</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>6</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Equivale a Educación Inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>MYC</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>5358</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Educación en Virtudes</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>7</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Equivale a Educación Inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>MYC</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>7408</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Inclusión y Dignidad de la Persona</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>7</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Equivale a Educación Inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>MYC</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>3681</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Metodología de la Investigación Cuantitativa</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>7</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Equivale a Educación Inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>MYC</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>9639</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Educación en el Bien, la Verdad y la Belleza</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>8</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Equivale a Educación Inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>MYC</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>4966</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ética Profesional</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>8</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Equivale a Educación Inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>MYC</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>7748</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Enseñanza Social de la Iglesia</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>8</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Equivale a Educación Inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>MYC</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>3480</v>
+      </c>
+      <c r="C62" t="inlineStr">
         <is>
           <t>Taller de Investigación Cualitativa
 Taller de Investigación Cuantitativa</t>
         </is>
       </c>
-      <c r="D30" t="n">
-        <v>8</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>LLYA</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>3312</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Taller de Proyectos Educativos</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>9</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>LLYA</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>1087</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Taller de Tesis I</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>9</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>LLYA</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>1490</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Electivo</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>9</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>LLYA</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>9845</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Gestión y Políticas Públicas Educativas</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>10</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>LLYA</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>8373</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Taller de Tesis II</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>10</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>MYC</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>4337</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Historia de la Educación</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>1</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>MYC</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>8012</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Fundamentos Neurobiológicos del Aprendizaje</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>1</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>MYC</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>7821</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Comunicación I</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>1</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>MYC</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>9160</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Literatura y Teatro</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>1</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>MYC</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>2557</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Familia y Escuela</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>MYC</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>4072</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Filosofía de la Educación</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>2</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>MYC</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>7854</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Comunicación II</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>2</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>MYC</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>9296</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Lógica</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>2</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>MYC</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>2778</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Música y Artes Visuales</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>2</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>MYC</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>8518</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Teorías y Enfoques Curriculares</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>3</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>MYC</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>6469</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Epistemología de la Educación</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>3</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>MYC</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>8401</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Filosofía de la Naturaleza</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>3</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>MYC</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>8762</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Antropología</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>3</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>MYC</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>3079</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Planificación de la Enseñanza</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>4</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>MYC</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>1512</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Evaluación</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>4</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>MYC</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>3132</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Antropología Pedagógica</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>4</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>MYC</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>1793</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Educación de la Afectividad</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>4</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>MYC</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>9953</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Sociología de la Educación</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>5</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>MYC</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>3064</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Moral</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>5</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>MYC</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>2301</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Análisis de la Realidad Peruana</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>5</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>MYC</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>2738</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Introducción a la Investigación Científica</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>5</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>MYC</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>2123</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Metodología de la Investigación Cualitativa</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>6</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>MYC</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>5358</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Educación en Virtudes</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>7</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>MYC</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>7408</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Inclusión y Dignidad de la Persona</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>7</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>MYC</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>3681</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Metodología de la Investigación Cuantitativa</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>7</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>MYC</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
-        <v>9639</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Educación en el Bien, la Verdad y la Belleza</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>8</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>MYC</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>4966</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ética Profesional</t>
-        </is>
-      </c>
       <c r="D62" t="n">
         <v>8</v>
       </c>
@@ -2172,15 +2173,15 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>7748</v>
+        <v>3322</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Enseñanza Social de la Iglesia</t>
+          <t>Taller de Proyectos Educativos</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2195,16 +2196,15 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>3480</v>
+        <v>6759</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Taller de Investigación Cualitativa
-Taller de Investigación Cuantitativa</t>
+          <t>Taller de Tesis I</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2219,11 +2219,11 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>3322</v>
+        <v>2791</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Taller de Proyectos Educativos</t>
+          <t>Electivo</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2242,15 +2242,15 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>6759</v>
+        <v>7324</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Taller de Tesis I</t>
+          <t>Gestión y Políticas Públicas Educativas</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2265,63 +2265,17 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>2791</v>
+        <v>3256</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Electivo</t>
+          <t>Taller de Tesis II</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E67" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>MYC</t>
-        </is>
-      </c>
-      <c r="B68" t="n">
-        <v>7324</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Gestión y Políticas Públicas Educativas</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>10</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Equivale a Educación Inicial</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>MYC</t>
-        </is>
-      </c>
-      <c r="B69" t="n">
-        <v>3256</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Taller de Tesis II</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>10</v>
-      </c>
-      <c r="E69" t="inlineStr">
         <is>
           <t>Equivale a Educación Inicial</t>
         </is>
@@ -2338,7 +2292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -2524,20 +2478,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Tutoría</t>
+          <t>Moral</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8636</v>
+        <v>3064</v>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>8636</v>
+        <v>3215</v>
       </c>
       <c r="E6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -2588,20 +2542,20 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Gestión de Instituciones Educativas y Liderazgo Pedagógico</t>
+          <t>Tutoría</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9935</v>
+        <v>8636</v>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>2283</v>
+        <v>8636</v>
       </c>
       <c r="E8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2652,17 +2606,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Práctica de Ayudantía</t>
+          <t>Gestión de Instituciones Educativas y Liderazgo Pedagógico</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6050</v>
+        <v>9935</v>
       </c>
       <c r="C10" t="n">
         <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>1433</v>
+        <v>2283</v>
       </c>
       <c r="E10" t="n">
         <v>8</v>
@@ -2673,7 +2627,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -2705,7 +2659,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -2716,28 +2670,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Quechua</t>
+          <t>Práctica de Ayudantía</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6053</v>
+        <v>6050</v>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D12" t="n">
-        <v>1127</v>
+        <v>1433</v>
       </c>
       <c r="E12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Virtual</t>
+          <t>Aula</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -2772,6 +2726,38 @@
         <v>2</v>
       </c>
       <c r="H13" t="inlineStr">
+        <is>
+          <t>Fase prematuro: solo LLYA activo → cuenta sin fusión. Fase compartida: ambos activos → sección combinada LLYA+MYC. Fase solo MYC: MYC activo → cuenta sin fusión.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Quechua</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>6053</v>
+      </c>
+      <c r="C14" t="n">
+        <v>10</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1127</v>
+      </c>
+      <c r="E14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" t="inlineStr">
         <is>
           <t>Fase prematuro: solo LLYA activo → cuenta sin fusión. Fase compartida: ambos activos → sección combinada LLYA+MYC. Fase solo MYC: MYC activo → cuenta sin fusión.</t>
         </is>

--- a/salida/excel/reporte_cursos.xlsx
+++ b/salida/excel/reporte_cursos.xlsx
@@ -3923,11 +3923,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Laboratorio de Química</t>
+          <t>Aula</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -3944,11 +3944,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Aula</t>
+          <t>Laboratorio de Biología</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -4007,11 +4007,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Laboratorio de Química</t>
+          <t>Aula</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -4028,11 +4028,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Aula</t>
+          <t>Laboratorio de Química</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -4112,11 +4112,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Laboratorio de Química</t>
+          <t>Aula</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -4133,11 +4133,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Aula</t>
+          <t>Laboratorio de Química</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -4259,11 +4259,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Laboratorio de Física</t>
+          <t>Aula</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -4280,11 +4280,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Aula</t>
+          <t>Laboratorio de Física</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -4301,11 +4301,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Laboratorio de Química</t>
+          <t>Aula</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -4322,11 +4322,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Aula</t>
+          <t>Laboratorio de Biología</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -4406,11 +4406,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Laboratorio de Física</t>
+          <t>Aula</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -4427,11 +4427,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Aula</t>
+          <t>Laboratorio de Física</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -4511,11 +4511,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Laboratorio de Química</t>
+          <t>Aula</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -4532,11 +4532,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Aula</t>
+          <t>Laboratorio de Biología</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">

--- a/salida/excel/reporte_cursos.xlsx
+++ b/salida/excel/reporte_cursos.xlsx
@@ -3602,7 +3602,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Virtual</t>
+          <t>Aula</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -3623,7 +3623,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Virtual</t>
+          <t>Aula</t>
         </is>
       </c>
       <c r="E40" t="n">
